--- a/output/pdf_financials_xlsx/STC.xlsx
+++ b/output/pdf_financials_xlsx/STC.xlsx
@@ -8311,10 +8311,10 @@
         <v>2.285243</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>2.324176</v>
+        <v>2.510876</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>2.514154</v>
+        <v>2.543502</v>
       </c>
       <c r="M107" s="3" t="n">
         <v>1.788</v>
@@ -21109,7 +21109,11 @@
           <t>Warrant reserve (Note 11(i))</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -23682,7 +23686,11 @@
           <t>Warrant reserve (Note 11(i)) 186,700</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/STC.xlsx
+++ b/output/pdf_financials_xlsx/STC.xlsx
@@ -574,38 +574,60 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n">
-        <v>-0.026374</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>-0.018047</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>-0.026907</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>-0.026809</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <v>-0.017992</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>-0.002694</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>-0.00082</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>-0.001566</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>-0.013763</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>-0.05317</v>
-      </c>
-      <c r="N4" s="3" t="n">
-        <v>-0.049211</v>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
@@ -664,26 +686,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H5" s="3" t="n">
-        <v>0.046282</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>0.108761</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>0.09972200000000001</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>0.246783</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>1.384706</v>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>2.530537</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>2.465643</v>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
@@ -1547,37 +1583,37 @@
         <v>0</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0</v>
+        <v>-0.026374</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>0</v>
+        <v>-0.018047</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0</v>
+        <v>-0.026907</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0</v>
+        <v>-0.026809</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0</v>
+        <v>-0.017992</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0</v>
+        <v>-0.002694</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0</v>
+        <v>-0.00082</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0</v>
+        <v>-0.001566</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0</v>
+        <v>-0.013763</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>0</v>
+        <v>-0.05317</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>0</v>
+        <v>-0.049211</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>0</v>
@@ -2517,37 +2553,37 @@
         <v>5.532114</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>-3.946254</v>
+        <v>-3.91988</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>0.821085</v>
+        <v>0.839132</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>-4.831398</v>
+        <v>-4.804491</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.967597</v>
+        <v>0.994406</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0.60498</v>
+        <v>0.622972</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0.283392</v>
+        <v>0.286086</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>1.190574</v>
+        <v>1.191394</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>3.948465</v>
+        <v>3.950031</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>2.877951</v>
+        <v>2.891714</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>5.076363</v>
+        <v>5.129533</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>4.384</v>
+        <v>4.433211</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>-104.39</v>
@@ -2633,37 +2669,37 @@
         <v>5.532114</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>-2.134544</v>
+        <v>-2.10817</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>1.263924</v>
+        <v>1.281971</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>-4.424005</v>
+        <v>-4.397098</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>1.141725</v>
+        <v>1.168534</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>1.056986</v>
+        <v>1.074978</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1.026342</v>
+        <v>1.029036</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>1.95313</v>
+        <v>1.95395</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>5.720016</v>
+        <v>5.721582</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>7.291533</v>
+        <v>7.305296</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>12.024799</v>
+        <v>12.077969</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>16.447</v>
+        <v>16.496211</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>-72.78100000000001</v>
@@ -2691,37 +2727,37 @@
         <v>44.21971437626668</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>-17.99554424502639</v>
+        <v>-17.77319488894925</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>9.183578048504559</v>
+        <v>9.314706212097752</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>-34.16173121326981</v>
+        <v>-33.95395800737256</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>8.255971003715214</v>
+        <v>8.449830581668399</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>6.477405444254784</v>
+        <v>6.587663743563414</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>4.842772744104827</v>
+        <v>4.855484325402893</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>7.266024563480683</v>
+        <v>7.26907512342398</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>9.971846522623746</v>
+        <v>9.974576569472292</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>6.649976394355067</v>
+        <v>6.662528435896332</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>9.150060038333038</v>
+        <v>9.190518817913318</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>12.51836234520448</v>
+        <v>12.5558184848877</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>-32.44053986592498</v>
@@ -59845,7 +59881,7 @@
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
@@ -59944,7 +59980,7 @@
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
@@ -61219,7 +61255,7 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
@@ -61322,7 +61358,7 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
@@ -62322,7 +62358,7 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
@@ -62425,7 +62461,7 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
@@ -63496,7 +63532,7 @@
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
@@ -63991,7 +64027,7 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
@@ -64086,7 +64122,7 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
@@ -67498,7 +67534,7 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
@@ -67601,7 +67637,7 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">

--- a/output/pdf_financials_xlsx/STC.xlsx
+++ b/output/pdf_financials_xlsx/STC.xlsx
@@ -2611,40 +2611,40 @@
         <v>0</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>1.81171</v>
+        <v>1.889114</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0.442839</v>
+        <v>0.521294</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.407393</v>
+        <v>0.494612</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.174128</v>
+        <v>0.2486</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0.452006</v>
+        <v>0.554831</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0.74295</v>
+        <v>0.864598</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.762556</v>
+        <v>0.892506</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>1.771551</v>
+        <v>1.967866</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>4.413582</v>
+        <v>4.845127</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>6.948436</v>
+        <v>11.016153</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>12.063</v>
+        <v>15.46</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>31.609</v>
+        <v>38.07</v>
       </c>
       <c r="P34" s="3" t="n">
         <v>33.932</v>
@@ -2669,40 +2669,40 @@
         <v>5.532114</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>-2.10817</v>
+        <v>-2.030766</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>1.281971</v>
+        <v>1.360426</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>-4.397098</v>
+        <v>-4.309879</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>1.168534</v>
+        <v>1.243006</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>1.074978</v>
+        <v>1.177803</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1.029036</v>
+        <v>1.150684</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>1.95395</v>
+        <v>2.0839</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>5.721582</v>
+        <v>5.917897</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>7.305296</v>
+        <v>7.736841</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>12.077969</v>
+        <v>16.145686</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>16.496211</v>
+        <v>19.893211</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>-72.78100000000001</v>
+        <v>-66.31999999999999</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>1.974</v>
@@ -2727,40 +2727,40 @@
         <v>44.21971437626668</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>-17.77319488894925</v>
+        <v>-17.12063063787641</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>9.314706212097752</v>
+        <v>9.884754423695464</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>-33.95395800737256</v>
+        <v>-33.28046147319365</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>8.449830581668399</v>
+        <v>8.988347888890962</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>6.587663743563414</v>
+        <v>7.217794336405229</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>4.855484325402893</v>
+        <v>5.429477807862797</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>7.26907512342398</v>
+        <v>7.752514470535702</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>9.974576569472292</v>
+        <v>10.31681740412885</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>6.662528435896332</v>
+        <v>7.056103293625422</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>9.190518817913318</v>
+        <v>12.28577677348895</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>12.5558184848877</v>
+        <v>15.14138891637426</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>-32.44053986592498</v>
+        <v>-29.56069034374555</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>0.7816893042410802</v>
@@ -8825,49 +8825,49 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>1.889114</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.521294</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.494612</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.2486</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.554831</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.864598</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.892506</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>1.967866</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>4.845127</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>11.016153</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>15.46</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>38.07</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>42.439</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>40.674</v>
       </c>
       <c r="R115" s="3" t="n">
-        <v>0</v>
+        <v>39.398</v>
       </c>
     </row>
     <row r="116">
@@ -9551,19 +9551,19 @@
         <v>0</v>
       </c>
       <c r="N127" s="3" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="O127" s="3" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="P127" s="3" t="n">
-        <v>0</v>
+        <v>0.409</v>
       </c>
       <c r="Q127" s="3" t="n">
-        <v>0</v>
+        <v>0.393</v>
       </c>
       <c r="R127" s="3" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="128">
@@ -33432,7 +33432,11 @@
           <t>Depreciation of property and equipment 7</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -33527,7 +33531,11 @@
           <t>Depreciation of right-of-use assets 8</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>
@@ -33624,7 +33632,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -34301,7 +34309,11 @@
           <t>Loss on disposal of property and equipment 7,20</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -37187,7 +37199,11 @@
           <t>Loss on disposal of property and equipment 7</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E266" t="inlineStr">
         <is>
           <t>-</t>
@@ -38656,7 +38672,11 @@
           <t>Depreciation of property and equipment (Note 7)</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -38755,7 +38775,11 @@
           <t>Depreciation of right-of-use assets (Note 8)</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -38856,7 +38880,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -39656,7 +39680,11 @@
           <t>Loss on disposal of property and equipment (Note 7)</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -41743,7 +41771,11 @@
           <t>Depreciation of property and equipment (Note 5)</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>
@@ -41834,7 +41866,11 @@
           <t>Depreciation of right-of-use assets (Note 17)</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -41935,7 +41971,7 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -44077,7 +44113,11 @@
           <t>Depreciation of right-of-use assets (Note 15)</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E336" t="inlineStr">
         <is>
           <t>-</t>
@@ -49295,7 +49335,11 @@
           <t>Depreciation of property, plant and equipment (Note 5)</t>
         </is>
       </c>
-      <c r="D390" t="inlineStr"/>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E390" t="inlineStr">
         <is>
           <t>-</t>
@@ -51877,7 +51921,11 @@
           <t>Depreciation of property, plant and equipment (Note 6)</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr"/>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E416" t="inlineStr">
         <is>
           <t>-</t>
@@ -51978,7 +52026,7 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -55096,7 +55144,7 @@
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">

--- a/output/pdf_financials_xlsx/STC.xlsx
+++ b/output/pdf_financials_xlsx/STC.xlsx
@@ -5208,15 +5208,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C68" s="3" t="n">
+        <v>1.20719</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>1.389355</v>
       </c>
       <c r="E68" s="1" t="inlineStr">
         <is>
@@ -5300,15 +5296,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C69" s="3" t="n">
+        <v>0.75945</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>0.924848</v>
       </c>
       <c r="E69" s="1" t="inlineStr">
         <is>
@@ -8797,7 +8789,7 @@
         <v>3.904616</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>0.7669899999999999</v>
+        <v>0.282</v>
       </c>
       <c r="O114" s="3" t="n">
         <v>-110.78</v>
@@ -9246,34 +9238,34 @@
         <v>0</v>
       </c>
       <c r="I122" s="3" t="n">
-        <v>0</v>
+        <v>0.17854</v>
       </c>
       <c r="J122" s="3" t="n">
-        <v>0</v>
+        <v>0.231034</v>
       </c>
       <c r="K122" s="3" t="n">
-        <v>0</v>
+        <v>0.174137</v>
       </c>
       <c r="L122" s="3" t="n">
-        <v>0</v>
+        <v>0.407676</v>
       </c>
       <c r="M122" s="3" t="n">
-        <v>0</v>
+        <v>0.401977</v>
       </c>
       <c r="N122" s="3" t="n">
-        <v>0</v>
+        <v>3.758</v>
       </c>
       <c r="O122" s="3" t="n">
-        <v>0</v>
+        <v>9.929</v>
       </c>
       <c r="P122" s="3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q122" s="3" t="n">
-        <v>0</v>
+        <v>2.983</v>
       </c>
       <c r="R122" s="3" t="n">
-        <v>0</v>
+        <v>2.908</v>
       </c>
     </row>
     <row r="123">
@@ -9289,7 +9281,7 @@
         <v>0</v>
       </c>
       <c r="D123" s="3" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="E123" s="3" t="n">
         <v>0</v>
@@ -9417,16 +9409,16 @@
         <v>0</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>0.015843</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>0.012825</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>0.014605</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>0.044319</v>
       </c>
       <c r="L125" s="3" t="n">
         <v>0</v>
@@ -9438,16 +9430,16 @@
         <v>0</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>0.798</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>0.911</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>0.394</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>0.301</v>
       </c>
     </row>
     <row r="126">
@@ -9753,7 +9745,7 @@
         <v>0</v>
       </c>
       <c r="D131" s="3" t="n">
-        <v>0</v>
+        <v>-0.059625</v>
       </c>
       <c r="E131" s="3" t="n">
         <v>0</v>
@@ -34020,7 +34012,11 @@
           <t>Share-based compensation expense 17(ii)</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -34210,7 +34206,11 @@
           <t>Accretion expense 8</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -37001,7 +37001,11 @@
           <t>Accretion expense 8,14</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>
@@ -38076,7 +38080,11 @@
           <t>Accretion expense 14</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -38577,7 +38585,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E280" t="inlineStr">
         <is>
           <t>-</t>
@@ -39179,7 +39191,11 @@
           <t>Share-based compensation expense (Note 17(ii))</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E286" t="inlineStr">
         <is>
           <t>-</t>
@@ -39478,7 +39494,11 @@
           <t>Accretion expense (Note 14)</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr"/>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E289" t="inlineStr">
         <is>
           <t>-</t>
@@ -42151,7 +42171,11 @@
           <t>Deferred income tax expense (recovery) (Note 10)</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
           <t>-</t>
@@ -42250,7 +42274,11 @@
           <t>Share-based compensation expense (Note 11(ii))</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E317" t="inlineStr">
         <is>
           <t>-</t>
@@ -44319,7 +44347,11 @@
           <t>Deferred income tax recovery (Note 10)</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr"/>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr">
         <is>
           <t>-</t>
@@ -46077,7 +46109,11 @@
           <t>Accretion expense (Note 13)</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
           <t>-</t>
@@ -48446,7 +48482,11 @@
           <t>Share-based compensation expense (Note 10(ii))</t>
         </is>
       </c>
-      <c r="D381" t="inlineStr"/>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E381" t="inlineStr">
         <is>
           <t>-</t>
@@ -48545,7 +48585,11 @@
           <t>Accretion expense (Note 9)</t>
         </is>
       </c>
-      <c r="D382" t="inlineStr"/>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr">
         <is>
           <t>-</t>
@@ -49735,7 +49779,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E394" t="inlineStr">
         <is>
           <t>-</t>
@@ -51820,7 +51868,11 @@
           <t>Impairment loss on goodwill</t>
         </is>
       </c>
-      <c r="D415" t="inlineStr"/>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E415" t="inlineStr">
         <is>
           <t>-</t>
@@ -52640,7 +52692,11 @@
           <t>Purchase of intangible assets (Note 7)</t>
         </is>
       </c>
-      <c r="D423" t="inlineStr"/>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E423" t="inlineStr">
         <is>
           <t>-</t>
